--- a/pools-example-single-pool-8.xlsx
+++ b/pools-example-single-pool-8.xlsx
@@ -1631,7 +1631,7 @@
         <f>RANK(U14,$U$14:$U$21)+COUNTIF($U$13:U13,U14)</f>
       </c>
       <c r="U14" t="str">
-        <f>=(B14*1000000)-(C14*10000)+(D14*100)+(E14*1)-(F14*0.01)</f>
+        <f>(B14*1000000)-(C14*10000)+(D14*100)+(E14*1)-(F14*0.01)</f>
       </c>
     </row>
     <row r="15">
@@ -1657,7 +1657,7 @@
         <f>RANK(U15,$U$14:$U$21)+COUNTIF($U$13:U14,U15)</f>
       </c>
       <c r="U15" t="str">
-        <f>=(B15*1000000)-(C15*10000)+(D15*100)+(E15*1)-(F15*0.01)</f>
+        <f>(B15*1000000)-(C15*10000)+(D15*100)+(E15*1)-(F15*0.01)</f>
       </c>
     </row>
     <row r="16">
@@ -1683,7 +1683,7 @@
         <f>RANK(U16,$U$14:$U$21)+COUNTIF($U$13:U15,U16)</f>
       </c>
       <c r="U16" t="str">
-        <f>=(B16*1000000)-(C16*10000)+(D16*100)+(E16*1)-(F16*0.01)</f>
+        <f>(B16*1000000)-(C16*10000)+(D16*100)+(E16*1)-(F16*0.01)</f>
       </c>
     </row>
     <row r="17">
@@ -1709,7 +1709,7 @@
         <f>RANK(U17,$U$14:$U$21)+COUNTIF($U$13:U16,U17)</f>
       </c>
       <c r="U17" t="str">
-        <f>=(B17*1000000)-(C17*10000)+(D17*100)+(E17*1)-(F17*0.01)</f>
+        <f>(B17*1000000)-(C17*10000)+(D17*100)+(E17*1)-(F17*0.01)</f>
       </c>
     </row>
     <row r="18">
@@ -1735,7 +1735,7 @@
         <f>RANK(U18,$U$14:$U$21)+COUNTIF($U$13:U17,U18)</f>
       </c>
       <c r="U18" t="str">
-        <f>=(B18*1000000)-(C18*10000)+(D18*100)+(E18*1)-(F18*0.01)</f>
+        <f>(B18*1000000)-(C18*10000)+(D18*100)+(E18*1)-(F18*0.01)</f>
       </c>
     </row>
     <row r="19">
@@ -1761,7 +1761,7 @@
         <f>RANK(U19,$U$14:$U$21)+COUNTIF($U$13:U18,U19)</f>
       </c>
       <c r="U19" t="str">
-        <f>=(B19*1000000)-(C19*10000)+(D19*100)+(E19*1)-(F19*0.01)</f>
+        <f>(B19*1000000)-(C19*10000)+(D19*100)+(E19*1)-(F19*0.01)</f>
       </c>
     </row>
     <row r="20">
@@ -1787,7 +1787,7 @@
         <f>RANK(U20,$U$14:$U$21)+COUNTIF($U$13:U19,U20)</f>
       </c>
       <c r="U20" t="str">
-        <f>=(B20*1000000)-(C20*10000)+(D20*100)+(E20*1)-(F20*0.01)</f>
+        <f>(B20*1000000)-(C20*10000)+(D20*100)+(E20*1)-(F20*0.01)</f>
       </c>
     </row>
     <row r="21">
@@ -1813,7 +1813,7 @@
         <f>RANK(U21,$U$14:$U$21)+COUNTIF($U$13:U20,U21)</f>
       </c>
       <c r="U21" t="str">
-        <f>=(B21*1000000)-(C21*10000)+(D21*100)+(E21*1)-(F21*0.01)</f>
+        <f>(B21*1000000)-(C21*10000)+(D21*100)+(E21*1)-(F21*0.01)</f>
       </c>
     </row>
     <row r="24">

--- a/pools-example-single-pool-8.xlsx
+++ b/pools-example-single-pool-8.xlsx
@@ -330,7 +330,7 @@
       <family val="2"/>
       <b val="1"/>
       <color/>
-      <sz val="150"/>
+      <sz val="200"/>
     </font>
   </fonts>
   <fills count="6">
@@ -958,82 +958,82 @@
     <col customWidth="true" max="1" min="1" width="90"/>
   </cols>
   <sheetData>
-    <row r="1" ht="390" customHeight="true">
+    <row r="1" ht="409" customHeight="true">
       <c r="A1" s="30" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="2" ht="390" customHeight="true">
+    <row r="2" ht="409" customHeight="true">
       <c r="A2" s="30" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="3" ht="390" customHeight="true">
+    <row r="3" ht="409" customHeight="true">
       <c r="A3" s="30" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="4" ht="390" customHeight="true">
+    <row r="4" ht="409" customHeight="true">
       <c r="A4" s="30" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="5" ht="390" customHeight="true">
+    <row r="5" ht="409" customHeight="true">
       <c r="A5" s="30" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="6" ht="390" customHeight="true">
+    <row r="6" ht="409" customHeight="true">
       <c r="A6" s="30" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="7" ht="390" customHeight="true">
+    <row r="7" ht="409" customHeight="true">
       <c r="A7" s="30" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="8" ht="390" customHeight="true">
+    <row r="8" ht="409" customHeight="true">
       <c r="A8" s="30" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="9" ht="390" customHeight="true">
+    <row r="9" ht="409" customHeight="true">
       <c r="A9" s="30" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="10" ht="390" customHeight="true">
+    <row r="10" ht="409" customHeight="true">
       <c r="A10" s="30" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="11" ht="390" customHeight="true">
+    <row r="11" ht="409" customHeight="true">
       <c r="A11" s="30" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="12" ht="390" customHeight="true">
+    <row r="12" ht="409" customHeight="true">
       <c r="A12" s="30" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="13" ht="390" customHeight="true">
+    <row r="13" ht="409" customHeight="true">
       <c r="A13" s="30" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="14" ht="390" customHeight="true">
+    <row r="14" ht="409" customHeight="true">
       <c r="A14" s="30" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="15" ht="390" customHeight="true">
+    <row r="15" ht="409" customHeight="true">
       <c r="A15" s="30" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="16" ht="390" customHeight="true">
+    <row r="16" ht="409" customHeight="true">
       <c r="A16" s="30" t="s">
         <v>59</v>
       </c>

--- a/pools-example-single-pool-8.xlsx
+++ b/pools-example-single-pool-8.xlsx
@@ -330,7 +330,7 @@
       <family val="2"/>
       <b val="1"/>
       <color/>
-      <sz val="200"/>
+      <sz val="250"/>
     </font>
   </fonts>
   <fills count="6">
@@ -955,7 +955,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="90"/>
+    <col customWidth="true" max="1" min="1" width="110"/>
   </cols>
   <sheetData>
     <row r="1" ht="409" customHeight="true">

--- a/pools-example-single-pool-8.xlsx
+++ b/pools-example-single-pool-8.xlsx
@@ -19,6 +19,7 @@
   <definedNames>
     <definedName localSheetId="2" name="_xlnm.Print_Area">'Pool Draw'!$B$2:$F$16</definedName>
     <definedName localSheetId="3" name="_xlnm.Print_Area">'Pool Matches'!$A$1:$H$33</definedName>
+    <definedName localSheetId="5" name="_xlnm.Print_Area">'Tree 1'!$A$1:$E$13</definedName>
     <definedName localSheetId="6" name="_xlnm.Print_Area">'Names to Print A'!$A$1:$B$8</definedName>
     <definedName localSheetId="4" name="_xlnm.Print_Area">'Elimination Matches'!$A$1:$H$14</definedName>
   </definedNames>
@@ -1985,12 +1986,17 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" max="1" min="1" width="25"/>
-    <col customWidth="true" max="2" min="2" width="10"/>
-    <col customWidth="true" max="26" min="3" width="3.5"/>
+    <col customWidth="true" max="2" min="2" width="4"/>
+    <col customWidth="true" max="3" min="3" width="28"/>
+    <col customWidth="true" max="26" min="4" width="3.5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2001,17 +2007,6 @@
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
       <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
     </row>
     <row r="4">
       <c r="A4" s="24" t="str">
@@ -2076,10 +2071,10 @@
   </sheetData>
   <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <printOptions horizontalCentered="true" verticalCentered="true"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 

--- a/pools-example-single-pool-8.xlsx
+++ b/pools-example-single-pool-8.xlsx
@@ -525,7 +525,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="true" applyAlignment="false">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="false">

--- a/pools-example-single-pool-8.xlsx
+++ b/pools-example-single-pool-8.xlsx
@@ -90,6 +90,12 @@
     <t>Team Beta</t>
   </si>
   <si>
+    <t>Michael Lewis</t>
+  </si>
+  <si>
+    <t>Team Gamma</t>
+  </si>
+  <si>
     <t>Nathan Lee</t>
   </si>
   <si>
@@ -102,28 +108,22 @@
     <t>Team Epsilon</t>
   </si>
   <si>
+    <t>Paul Hall</t>
+  </si>
+  <si>
+    <t>Team Zeta</t>
+  </si>
+  <si>
     <t>Quentin Allen</t>
   </si>
   <si>
     <t>Team Eta</t>
   </si>
   <si>
-    <t>Michael Lewis</t>
-  </si>
-  <si>
-    <t>Team Gamma</t>
-  </si>
-  <si>
     <t>Robert Young</t>
   </si>
   <si>
     <t>Team Theta</t>
-  </si>
-  <si>
-    <t>Paul Hall</t>
-  </si>
-  <si>
-    <t>Team Zeta</t>
   </si>
   <si>
     <t>Shiaijo A</t>

--- a/pools-example-single-pool-8.xlsx
+++ b/pools-example-single-pool-8.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
   <si>
     <t>Number of pools</t>
   </si>
@@ -72,6 +72,9 @@
     <t>Player Dojo</t>
   </si>
   <si>
+    <t>Player Number</t>
+  </si>
+  <si>
     <t>Metadata</t>
   </si>
   <si>
@@ -84,48 +87,72 @@
     <t>Team Alpha</t>
   </si>
   <si>
+    <t>K1</t>
+  </si>
+  <si>
     <t>Luke Rodriguez</t>
   </si>
   <si>
     <t>Team Beta</t>
   </si>
   <si>
+    <t>K2</t>
+  </si>
+  <si>
     <t>Michael Lewis</t>
   </si>
   <si>
     <t>Team Gamma</t>
   </si>
   <si>
+    <t>K3</t>
+  </si>
+  <si>
     <t>Nathan Lee</t>
   </si>
   <si>
     <t>Team Delta</t>
   </si>
   <si>
+    <t>K4</t>
+  </si>
+  <si>
     <t>Oliver Walker</t>
   </si>
   <si>
     <t>Team Epsilon</t>
   </si>
   <si>
+    <t>K5</t>
+  </si>
+  <si>
     <t>Paul Hall</t>
   </si>
   <si>
     <t>Team Zeta</t>
   </si>
   <si>
+    <t>K6</t>
+  </si>
+  <si>
     <t>Quentin Allen</t>
   </si>
   <si>
     <t>Team Eta</t>
   </si>
   <si>
+    <t>K7</t>
+  </si>
+  <si>
     <t>Robert Young</t>
   </si>
   <si>
     <t>Team Theta</t>
   </si>
   <si>
+    <t>K8</t>
+  </si>
+  <si>
     <t>Shiaijo A</t>
   </si>
   <si>
@@ -184,30 +211,6 @@
   </si>
   <si>
     <t>8.</t>
-  </si>
-  <si>
-    <t>A1</t>
-  </si>
-  <si>
-    <t>A2</t>
-  </si>
-  <si>
-    <t>A3</t>
-  </si>
-  <si>
-    <t>A4</t>
-  </si>
-  <si>
-    <t>A5</t>
-  </si>
-  <si>
-    <t>A6</t>
-  </si>
-  <si>
-    <t>A7</t>
-  </si>
-  <si>
-    <t>A8</t>
   </si>
   <si>
     <t>Round 1 - Match 1</t>
@@ -854,96 +857,123 @@
       <c r="C2" t="s">
         <v>13</v>
       </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>27</v>
+      </c>
+      <c r="D6" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>30</v>
+      </c>
+      <c r="D7" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>33</v>
+      </c>
+      <c r="D8" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>36</v>
+      </c>
+      <c r="D9" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="C10" t="s">
-        <v>31</v>
+        <v>39</v>
+      </c>
+      <c r="D10" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -961,82 +991,82 @@
   <sheetData>
     <row r="1" ht="409" customHeight="true">
       <c r="A1" s="30" t="s">
-        <v>52</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" ht="409" customHeight="true">
       <c r="A2" s="30" t="s">
-        <v>52</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" ht="409" customHeight="true">
       <c r="A3" s="30" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" ht="409" customHeight="true">
       <c r="A4" s="30" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" ht="409" customHeight="true">
       <c r="A5" s="30" t="s">
-        <v>54</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" ht="409" customHeight="true">
       <c r="A6" s="30" t="s">
-        <v>54</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" ht="409" customHeight="true">
       <c r="A7" s="30" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" ht="409" customHeight="true">
       <c r="A8" s="30" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" ht="409" customHeight="true">
       <c r="A9" s="30" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" ht="409" customHeight="true">
       <c r="A10" s="30" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" ht="409" customHeight="true">
       <c r="A11" s="30" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" ht="409" customHeight="true">
       <c r="A12" s="30" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" ht="409" customHeight="true">
       <c r="A13" s="30" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" ht="409" customHeight="true">
       <c r="A14" s="30" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" ht="409" customHeight="true">
       <c r="A15" s="30" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" ht="409" customHeight="true">
       <c r="A16" s="30" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1257,7 +1287,7 @@
     </row>
     <row r="13">
       <c r="E13" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F13" s="13"/>
       <c r="G13" s="13"/>
@@ -1268,7 +1298,7 @@
         <v>1</v>
       </c>
       <c r="E14" s="32" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F14" s="32"/>
       <c r="G14" s="32"/>
@@ -1278,7 +1308,7 @@
     </row>
     <row r="15">
       <c r="E15" s="32" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F15" s="32"/>
       <c r="G15" s="32"/>
@@ -1288,7 +1318,7 @@
     </row>
     <row r="16">
       <c r="E16" s="32" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F16" s="32"/>
       <c r="G16" s="32"/>
@@ -1298,7 +1328,7 @@
     </row>
     <row r="17">
       <c r="E17" s="32" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F17" s="32"/>
       <c r="G17" s="32"/>
@@ -1308,7 +1338,7 @@
     </row>
     <row r="18">
       <c r="E18" s="13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F18" s="13"/>
       <c r="G18" s="13"/>
@@ -1318,7 +1348,7 @@
     </row>
     <row r="19">
       <c r="E19" s="13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F19" s="13"/>
       <c r="G19" s="13"/>
@@ -1383,42 +1413,42 @@
     </row>
     <row r="6" ht="17" customHeight="true">
       <c r="B6" s="12" t="str">
-        <f>"1. " &amp; data!$B$3</f>
+        <f>data!$D$3&amp;" "&amp;data!$B$3</f>
       </c>
     </row>
     <row r="7" ht="17" customHeight="true">
       <c r="B7" s="12" t="str">
-        <f>"2. " &amp; data!$B$4</f>
+        <f>data!$D$4&amp;" "&amp;data!$B$4</f>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="12" t="str">
-        <f>"3. " &amp; data!$B$5</f>
+        <f>data!$D$5&amp;" "&amp;data!$B$5</f>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="12" t="str">
-        <f>"4. " &amp; data!$B$6</f>
+        <f>data!$D$6&amp;" "&amp;data!$B$6</f>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="12" t="str">
-        <f>"5. " &amp; data!$B$7</f>
+        <f>data!$D$7&amp;" "&amp;data!$B$7</f>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="12" t="str">
-        <f>"6. " &amp; data!$B$8</f>
+        <f>data!$D$8&amp;" "&amp;data!$B$8</f>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="12" t="str">
-        <f>"7. " &amp; data!$B$9</f>
+        <f>data!$D$9&amp;" "&amp;data!$B$9</f>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="12" t="str">
-        <f>"8. " &amp; data!$B$10</f>
+        <f>data!$D$10&amp;" "&amp;data!$B$10</f>
       </c>
     </row>
   </sheetData>
@@ -1451,7 +1481,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="13" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
@@ -1473,18 +1503,18 @@
     </row>
     <row r="3">
       <c r="A3" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="14" t="str">
-        <f>'data'!$B$4</f>
+        <f>data!$D$4&amp;" "&amp;data!$B$4</f>
       </c>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -1492,12 +1522,12 @@
       <c r="E4" s="18"/>
       <c r="F4" s="18"/>
       <c r="G4" s="14" t="str">
-        <f>'data'!$B$3</f>
+        <f>data!$D$3&amp;" "&amp;data!$B$3</f>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="14" t="str">
-        <f>'data'!$B$4</f>
+        <f>data!$D$4&amp;" "&amp;data!$B$4</f>
       </c>
       <c r="B5" s="18"/>
       <c r="C5" s="18"/>
@@ -1505,12 +1535,12 @@
       <c r="E5" s="18"/>
       <c r="F5" s="18"/>
       <c r="G5" s="14" t="str">
-        <f>'data'!$B$5</f>
+        <f>data!$D$5&amp;" "&amp;data!$B$5</f>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="14" t="str">
-        <f>'data'!$B$6</f>
+        <f>data!$D$6&amp;" "&amp;data!$B$6</f>
       </c>
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
@@ -1518,12 +1548,12 @@
       <c r="E6" s="18"/>
       <c r="F6" s="18"/>
       <c r="G6" s="14" t="str">
-        <f>'data'!$B$5</f>
+        <f>data!$D$5&amp;" "&amp;data!$B$5</f>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="str">
-        <f>'data'!$B$6</f>
+        <f>data!$D$6&amp;" "&amp;data!$B$6</f>
       </c>
       <c r="B7" s="18"/>
       <c r="C7" s="18"/>
@@ -1531,12 +1561,12 @@
       <c r="E7" s="18"/>
       <c r="F7" s="18"/>
       <c r="G7" s="14" t="str">
-        <f>'data'!$B$7</f>
+        <f>data!$D$7&amp;" "&amp;data!$B$7</f>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="str">
-        <f>'data'!$B$8</f>
+        <f>data!$D$8&amp;" "&amp;data!$B$8</f>
       </c>
       <c r="B8" s="18"/>
       <c r="C8" s="18"/>
@@ -1544,12 +1574,12 @@
       <c r="E8" s="18"/>
       <c r="F8" s="18"/>
       <c r="G8" s="14" t="str">
-        <f>'data'!$B$7</f>
+        <f>data!$D$7&amp;" "&amp;data!$B$7</f>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="str">
-        <f>'data'!$B$8</f>
+        <f>data!$D$8&amp;" "&amp;data!$B$8</f>
       </c>
       <c r="B9" s="18"/>
       <c r="C9" s="18"/>
@@ -1557,12 +1587,12 @@
       <c r="E9" s="18"/>
       <c r="F9" s="18"/>
       <c r="G9" s="14" t="str">
-        <f>'data'!$B$9</f>
+        <f>data!$D$9&amp;" "&amp;data!$B$9</f>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="14" t="str">
-        <f>'data'!$B$10</f>
+        <f>data!$D$10&amp;" "&amp;data!$B$10</f>
       </c>
       <c r="B10" s="18"/>
       <c r="C10" s="18"/>
@@ -1570,12 +1600,12 @@
       <c r="E10" s="18"/>
       <c r="F10" s="18"/>
       <c r="G10" s="14" t="str">
-        <f>'data'!$B$9</f>
+        <f>data!$D$9&amp;" "&amp;data!$B$9</f>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="str">
-        <f>'data'!$B$10</f>
+        <f>data!$D$10&amp;" "&amp;data!$B$10</f>
       </c>
       <c r="B11" s="18"/>
       <c r="C11" s="18"/>
@@ -1583,35 +1613,35 @@
       <c r="E11" s="18"/>
       <c r="F11" s="18"/>
       <c r="G11" s="14" t="str">
-        <f>'data'!$B$3</f>
+        <f>data!$D$3&amp;" "&amp;data!$B$3</f>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="13" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="14" t="str">
-        <f>'data'!$B$3</f>
+        <f>data!$D$3&amp;" "&amp;data!$B$3</f>
       </c>
       <c r="B14" s="14" t="str">
         <f>IF(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),IF(OR(D4="X",D4="x",AND(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C4," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F4," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F4," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C4," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B11,C11,E11,F11)&gt;0,OR(D11="X",D11="x")),IF(OR(D11="X",D11="x",AND(OR(COUNTA(B11,C11,E11,F11)&gt;0,OR(D11="X",D11="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B11," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C11," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E11," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F11," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E11," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F11," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B11," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C11," ",""),"0",""),"-","")))*1),0)</f>
@@ -1637,7 +1667,7 @@
     </row>
     <row r="15">
       <c r="A15" s="14" t="str">
-        <f>'data'!$B$4</f>
+        <f>data!$D$4&amp;" "&amp;data!$B$4</f>
       </c>
       <c r="B15" s="14" t="str">
         <f>IF(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),IF(OR(D4="X",D4="x",AND(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C4," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F4," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C4," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F4," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),IF(OR(D5="X",D5="x",AND(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")))*1),0)</f>
@@ -1663,7 +1693,7 @@
     </row>
     <row r="16">
       <c r="A16" s="14" t="str">
-        <f>'data'!$B$5</f>
+        <f>data!$D$5&amp;" "&amp;data!$B$5</f>
       </c>
       <c r="B16" s="14" t="str">
         <f>IF(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),IF(OR(D5="X",D5="x",AND(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),IF(OR(D6="X",D6="x",AND(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")))*1),0)</f>
@@ -1689,7 +1719,7 @@
     </row>
     <row r="17">
       <c r="A17" s="14" t="str">
-        <f>'data'!$B$6</f>
+        <f>data!$D$6&amp;" "&amp;data!$B$6</f>
       </c>
       <c r="B17" s="14" t="str">
         <f>IF(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),IF(OR(D6="X",D6="x",AND(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B7,C7,E7,F7)&gt;0,OR(D7="X",D7="x")),IF(OR(D7="X",D7="x",AND(OR(COUNTA(B7,C7,E7,F7)&gt;0,OR(D7="X",D7="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-","")))*1),0)</f>
@@ -1715,7 +1745,7 @@
     </row>
     <row r="18">
       <c r="A18" s="14" t="str">
-        <f>'data'!$B$7</f>
+        <f>data!$D$7&amp;" "&amp;data!$B$7</f>
       </c>
       <c r="B18" s="14" t="str">
         <f>IF(OR(COUNTA(B7,C7,E7,F7)&gt;0,OR(D7="X",D7="x")),IF(OR(D7="X",D7="x",AND(OR(COUNTA(B7,C7,E7,F7)&gt;0,OR(D7="X",D7="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B8,C8,E8,F8)&gt;0,OR(D8="X",D8="x")),IF(OR(D8="X",D8="x",AND(OR(COUNTA(B8,C8,E8,F8)&gt;0,OR(D8="X",D8="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-","")))*1),0)</f>
@@ -1741,7 +1771,7 @@
     </row>
     <row r="19">
       <c r="A19" s="14" t="str">
-        <f>'data'!$B$8</f>
+        <f>data!$D$8&amp;" "&amp;data!$B$8</f>
       </c>
       <c r="B19" s="14" t="str">
         <f>IF(OR(COUNTA(B8,C8,E8,F8)&gt;0,OR(D8="X",D8="x")),IF(OR(D8="X",D8="x",AND(OR(COUNTA(B8,C8,E8,F8)&gt;0,OR(D8="X",D8="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B9,C9,E9,F9)&gt;0,OR(D9="X",D9="x")),IF(OR(D9="X",D9="x",AND(OR(COUNTA(B9,C9,E9,F9)&gt;0,OR(D9="X",D9="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-","")))*1),0)</f>
@@ -1767,7 +1797,7 @@
     </row>
     <row r="20">
       <c r="A20" s="14" t="str">
-        <f>'data'!$B$9</f>
+        <f>data!$D$9&amp;" "&amp;data!$B$9</f>
       </c>
       <c r="B20" s="14" t="str">
         <f>IF(OR(COUNTA(B9,C9,E9,F9)&gt;0,OR(D9="X",D9="x")),IF(OR(D9="X",D9="x",AND(OR(COUNTA(B9,C9,E9,F9)&gt;0,OR(D9="X",D9="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B10,C10,E10,F10)&gt;0,OR(D10="X",D10="x")),IF(OR(D10="X",D10="x",AND(OR(COUNTA(B10,C10,E10,F10)&gt;0,OR(D10="X",D10="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B10," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C10," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E10," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F10," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E10," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F10," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B10," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C10," ",""),"0",""),"-","")))*1),0)</f>
@@ -1793,7 +1823,7 @@
     </row>
     <row r="21">
       <c r="A21" s="14" t="str">
-        <f>'data'!$B$10</f>
+        <f>data!$D$10&amp;" "&amp;data!$B$10</f>
       </c>
       <c r="B21" s="14" t="str">
         <f>IF(OR(COUNTA(B10,C10,E10,F10)&gt;0,OR(D10="X",D10="x")),IF(OR(D10="X",D10="x",AND(OR(COUNTA(B10,C10,E10,F10)&gt;0,OR(D10="X",D10="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B10," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C10," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E10," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F10," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B10," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C10," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E10," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F10," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B11,C11,E11,F11)&gt;0,OR(D11="X",D11="x")),IF(OR(D11="X",D11="x",AND(OR(COUNTA(B11,C11,E11,F11)&gt;0,OR(D11="X",D11="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B11," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C11," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E11," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F11," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B11," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C11," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E11," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F11," ",""),"0",""),"-","")))*1),0)</f>
@@ -1820,12 +1850,12 @@
     <row r="24">
       <c r="F24" s="13"/>
       <c r="G24" s="13" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
     </row>
     <row r="25">
       <c r="F25" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="G25" s="19" t="str">
         <f>IFERROR(INDEX($A$14:$A$21, MATCH(1, $G$14:$G$21, 0)), "-")</f>
@@ -1833,7 +1863,7 @@
     </row>
     <row r="26">
       <c r="F26" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="G26" s="19" t="str">
         <f>IFERROR(INDEX($A$14:$A$21, MATCH(2, $G$14:$G$21, 0)), "-")</f>
@@ -1841,7 +1871,7 @@
     </row>
     <row r="27">
       <c r="F27" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="G27" s="19" t="str">
         <f>IFERROR(INDEX($A$14:$A$21, MATCH(3, $G$14:$G$21, 0)), "-")</f>
@@ -1849,7 +1879,7 @@
     </row>
     <row r="28">
       <c r="F28" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="G28" s="19" t="str">
         <f>IFERROR(INDEX($A$14:$A$21, MATCH(4, $G$14:$G$21, 0)), "-")</f>
@@ -1857,7 +1887,7 @@
     </row>
     <row r="29">
       <c r="F29" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="G29" s="19" t="str">
         <f>IFERROR(INDEX($A$14:$A$21, MATCH(5, $G$14:$G$21, 0)), "-")</f>
@@ -1865,7 +1895,7 @@
     </row>
     <row r="30">
       <c r="F30" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="G30" s="19" t="str">
         <f>IFERROR(INDEX($A$14:$A$21, MATCH(6, $G$14:$G$21, 0)), "-")</f>
@@ -1873,7 +1903,7 @@
     </row>
     <row r="31">
       <c r="F31" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="G31" s="19" t="str">
         <f>IFERROR(INDEX($A$14:$A$21, MATCH(7, $G$14:$G$21, 0)), "-")</f>
@@ -1881,7 +1911,7 @@
     </row>
     <row r="32">
       <c r="F32" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="G32" s="19" t="str">
         <f>IFERROR(INDEX($A$14:$A$21, MATCH(8, $G$14:$G$21, 0)), "-")</f>
@@ -1918,7 +1948,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="13" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
@@ -1929,7 +1959,7 @@
     </row>
     <row r="2">
       <c r="A2" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
@@ -1940,13 +1970,13 @@
     </row>
     <row r="3">
       <c r="A3" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4">
@@ -1964,13 +1994,13 @@
     </row>
     <row r="6">
       <c r="F6" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="G6" s="19"/>
     </row>
     <row r="7">
       <c r="F7" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="G7" s="19"/>
     </row>
@@ -2015,7 +2045,7 @@
     </row>
     <row r="5">
       <c r="A5" s="25" t="str">
-        <f>"1. " &amp; data!$B$3</f>
+        <f>data!$D$3&amp;" "&amp;data!$B$3</f>
       </c>
       <c r="C5" s="23" t="str">
         <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G25)</f>
@@ -2023,7 +2053,7 @@
     </row>
     <row r="6">
       <c r="A6" s="26" t="str">
-        <f>"2. " &amp; data!$B$4</f>
+        <f>data!$D$4&amp;" "&amp;data!$B$4</f>
       </c>
       <c r="D6" s="22"/>
       <c r="E6" s="21">
@@ -2032,7 +2062,7 @@
     </row>
     <row r="7">
       <c r="A7" s="26" t="str">
-        <f>"3. " &amp; data!$B$5</f>
+        <f>data!$D$5&amp;" "&amp;data!$B$5</f>
       </c>
       <c r="C7" s="23" t="str">
         <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G26)</f>
@@ -2042,27 +2072,27 @@
     </row>
     <row r="8">
       <c r="A8" s="26" t="str">
-        <f>"4. " &amp; data!$B$6</f>
+        <f>data!$D$6&amp;" "&amp;data!$B$6</f>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="26" t="str">
-        <f>"5. " &amp; data!$B$7</f>
+        <f>data!$D$7&amp;" "&amp;data!$B$7</f>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="26" t="str">
-        <f>"6. " &amp; data!$B$8</f>
+        <f>data!$D$8&amp;" "&amp;data!$B$8</f>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="26" t="str">
-        <f>"7. " &amp; data!$B$9</f>
+        <f>data!$D$9&amp;" "&amp;data!$B$9</f>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="27" t="str">
-        <f>"8. " &amp; data!$B$10</f>
+        <f>data!$D$10&amp;" "&amp;data!$B$10</f>
       </c>
     </row>
     <row r="13">
@@ -2087,64 +2117,64 @@
   </cols>
   <sheetData>
     <row r="1" ht="270" customHeight="true">
-      <c r="A1" s="28" t="s">
-        <v>52</v>
+      <c r="A1" s="28" t="str">
+        <f>'data'!$D$3</f>
       </c>
       <c r="B1" s="29" t="str">
         <f>'data'!$B$3</f>
       </c>
     </row>
     <row r="2" ht="270" customHeight="true">
-      <c r="A2" s="28" t="s">
-        <v>53</v>
+      <c r="A2" s="28" t="str">
+        <f>'data'!$D$4</f>
       </c>
       <c r="B2" s="29" t="str">
         <f>'data'!$B$4</f>
       </c>
     </row>
     <row r="3" ht="270" customHeight="true">
-      <c r="A3" s="28" t="s">
-        <v>54</v>
+      <c r="A3" s="28" t="str">
+        <f>'data'!$D$5</f>
       </c>
       <c r="B3" s="29" t="str">
         <f>'data'!$B$5</f>
       </c>
     </row>
     <row r="4" ht="270" customHeight="true">
-      <c r="A4" s="28" t="s">
-        <v>55</v>
+      <c r="A4" s="28" t="str">
+        <f>'data'!$D$6</f>
       </c>
       <c r="B4" s="29" t="str">
         <f>'data'!$B$6</f>
       </c>
     </row>
     <row r="5" ht="270" customHeight="true">
-      <c r="A5" s="28" t="s">
-        <v>56</v>
+      <c r="A5" s="28" t="str">
+        <f>'data'!$D$7</f>
       </c>
       <c r="B5" s="29" t="str">
         <f>'data'!$B$7</f>
       </c>
     </row>
     <row r="6" ht="270" customHeight="true">
-      <c r="A6" s="28" t="s">
-        <v>57</v>
+      <c r="A6" s="28" t="str">
+        <f>'data'!$D$8</f>
       </c>
       <c r="B6" s="29" t="str">
         <f>'data'!$B$8</f>
       </c>
     </row>
     <row r="7" ht="270" customHeight="true">
-      <c r="A7" s="28" t="s">
-        <v>58</v>
+      <c r="A7" s="28" t="str">
+        <f>'data'!$D$9</f>
       </c>
       <c r="B7" s="29" t="str">
         <f>'data'!$B$9</f>
       </c>
     </row>
     <row r="8" ht="270" customHeight="true">
-      <c r="A8" s="28" t="s">
-        <v>59</v>
+      <c r="A8" s="28" t="str">
+        <f>'data'!$D$10</f>
       </c>
       <c r="B8" s="29" t="str">
         <f>'data'!$B$10</f>

--- a/pools-example-single-pool-8.xlsx
+++ b/pools-example-single-pool-8.xlsx
@@ -21,6 +21,7 @@
     <definedName localSheetId="3" name="_xlnm.Print_Area">'Pool Matches'!$A$1:$H$33</definedName>
     <definedName localSheetId="5" name="_xlnm.Print_Area">'Tree 1'!$A$1:$E$13</definedName>
     <definedName localSheetId="6" name="_xlnm.Print_Area">'Names to Print A'!$A$1:$B$8</definedName>
+    <definedName localSheetId="7" name="_xlnm.Print_Area">'Tags'!$A$1:$A$16</definedName>
     <definedName localSheetId="4" name="_xlnm.Print_Area">'Elimination Matches'!$A$1:$H$14</definedName>
   </definedNames>
   <calcPr calcId="122211"/>
@@ -544,13 +545,13 @@
       <alignment/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
@@ -986,7 +987,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="110"/>
+    <col customWidth="true" max="1" min="1" width="88"/>
   </cols>
   <sheetData>
     <row r="1" ht="409" customHeight="true">

--- a/pools-example-single-pool-8.xlsx
+++ b/pools-example-single-pool-8.xlsx
@@ -548,7 +548,7 @@
       <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
       <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
@@ -2113,8 +2113,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="30"/>
-    <col customWidth="true" max="2" min="2" width="160"/>
+    <col customWidth="true" max="1" min="1" width="40"/>
+    <col customWidth="true" max="2" min="2" width="140"/>
   </cols>
   <sheetData>
     <row r="1" ht="270" customHeight="true">

--- a/pools-example-single-pool-8.xlsx
+++ b/pools-example-single-pool-8.xlsx
@@ -551,7 +551,7 @@
       <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
+      <alignment horizontal="center" shrinkToFit="true" vertical="top"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
